--- a/src/assets/大批匯入車籍-範例.xlsx
+++ b/src/assets/大批匯入車籍-範例.xlsx
@@ -14,14 +14,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>客戶代號</t>
   </si>
   <si>
-    <t>統一編號</t>
-  </si>
-  <si>
     <t>車號</t>
   </si>
   <si>
@@ -31,9 +28,6 @@
     <t>G1308719</t>
   </si>
   <si>
-    <t>A130871992</t>
-  </si>
-  <si>
     <t>VFP-6188</t>
   </si>
   <si>
@@ -44,11 +38,27 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>油品(0001，0002，0005，0006，0017多種油品請用'，'區隔)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0001,0017</t>
+    <t>VFP-6189</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>統一編號(無統編輸入0)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>13087199</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>油品(0001，0002，0005，0006)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0006</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -423,7 +433,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="68.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
@@ -436,50 +446,50 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/大批匯入車籍-範例.xlsx
+++ b/src/assets/大批匯入車籍-範例.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>客戶代號</t>
   </si>
@@ -35,43 +35,67 @@
   </si>
   <si>
     <t>0001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>VFP-6189</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>統一編號(無統編輸入0)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>13087199</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>0</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>油品(0001，0002，0005，0006)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>0006</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>客戶名稱</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>精誠資訊測試</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -135,13 +159,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -429,71 +459,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="68.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="37.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
